--- a/data/trans_camb/P15B_tráfico-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15B_tráfico-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,15</t>
+          <t>23,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,4</t>
+          <t>-12,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>4,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 54,13</t>
+          <t>-6,87; 52,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 38,56</t>
+          <t>-25,46; 38,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 60,23</t>
+          <t>-11,88; 49,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 31,22</t>
+          <t>-42,67; 35,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 27,73</t>
+          <t>-51,6; 28,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 17,28</t>
+          <t>-53,24; 15,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 38,03</t>
+          <t>-14,36; 35,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 26,56</t>
+          <t>-22,68; 25,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 31,87</t>
+          <t>-23,66; 25,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>145,15%</t>
+          <t>119,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-41,27%</t>
+          <t>-46,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,6; —</t>
+          <t>-22,17; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,41; —</t>
+          <t>-76,56; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,42; —</t>
+          <t>-39,69; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,07; —</t>
+          <t>-74,09; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,46; —</t>
+          <t>-78,04; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,75; —</t>
+          <t>-86,48; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 580,63</t>
+          <t>-34,52; 504,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 429,41</t>
+          <t>-56,58; 356,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 471,29</t>
+          <t>-55,7; 398,05</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-51,54</t>
+          <t>-52,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,91</t>
+          <t>-15,23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-33,91</t>
+          <t>-33,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-69,6; -8,54</t>
+          <t>-70,02; -1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-93,95; -26,04</t>
+          <t>-93,8; -24,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-81,03; -8,27</t>
+          <t>-81,99; -6,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 17,77</t>
+          <t>-53,84; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 29,39</t>
+          <t>-53,43; 26,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 12,09</t>
+          <t>-52,6; 14,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 1,92</t>
+          <t>-53,06; -1,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,18; -4,12</t>
+          <t>-63,89; -8,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-60,08; -3,82</t>
+          <t>-62,28; -9,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-59,41%</t>
+          <t>-60,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-50,13%</t>
+          <t>-45,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-57,97%</t>
+          <t>-57,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,33; -19,93</t>
+          <t>-74,41; -16,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,28; -45,22</t>
+          <t>-94,26; -45,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,03; -12,59</t>
+          <t>-86,34; -13,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 177,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,27; —</t>
+          <t>-88,32; 248,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,41; 136,59</t>
+          <t>-84,58; 263,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 6,67</t>
+          <t>-71,09; -5,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,21; -3,87</t>
+          <t>-84,0; -20,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,13; -8,75</t>
+          <t>-78,65; -20,11</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-22,44</t>
+          <t>-23,47</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-13,34</t>
+          <t>-14,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-54,83; -3,01</t>
+          <t>-54,5; -3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 16,44</t>
+          <t>-44,76; 14,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 2,95</t>
+          <t>-55,73; 0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 27,96</t>
+          <t>2,51; 27,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,51</t>
+          <t>0,0; 33,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 33,55</t>
+          <t>5,51; 33,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,21; -0,14</t>
+          <t>-45,45; -1,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 14,23</t>
+          <t>-38,75; 13,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 6,51</t>
+          <t>-39,24; 6,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-64,72%</t>
+          <t>-67,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-47,35%</t>
+          <t>-50,07%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-96,25; 2,71</t>
+          <t>-96,73; -5,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 109,55</t>
+          <t>-80,39; 123,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,94</t>
+          <t>-99,78; 42,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 25,39</t>
+          <t>-90,29; -0,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 171,19</t>
+          <t>-78,41; 122,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 81,14</t>
+          <t>-83,04; 70,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>21,08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,16</t>
+          <t>19,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>21,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 37,96</t>
+          <t>-9,38; 36,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 26,74</t>
+          <t>-12,59; 26,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 49,11</t>
+          <t>-5,44; 54,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-65,69; 0,71</t>
+          <t>-63,59; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,11; -9,63</t>
+          <t>-68,47; -9,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 57,29</t>
+          <t>-20,83; 58,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 16,79</t>
+          <t>-22,46; 18,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 5,18</t>
+          <t>-28,86; 5,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 44,45</t>
+          <t>-4,69; 45,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140,42%</t>
+          <t>198,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>114,22%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,52; —</t>
+          <t>-73,48; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,25; —</t>
+          <t>-83,52; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,32; —</t>
+          <t>-69,27; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 596,85</t>
+          <t>-54,69; 557,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 199,28</t>
+          <t>-73,65; 259,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-85,27; 90,74</t>
+          <t>-85,46; 79,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 583,67</t>
+          <t>-21,39; 570,02</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 48,27</t>
+          <t>-15,68; 50,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 36,39</t>
+          <t>-35,57; 36,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 40,05</t>
+          <t>-27,67; 44,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 56,88</t>
+          <t>-27,98; 53,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 0,0</t>
+          <t>-66,24; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 46,44</t>
+          <t>-10,11; 43,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 19,38</t>
+          <t>-31,94; 19,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 36,43</t>
+          <t>-26,94; 40,18</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,01; —</t>
+          <t>-52,63; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 864,72</t>
+          <t>-32,2; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>11,37</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>8,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>13,25; 50,86</t>
+          <t>13,95; 49,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,53; 34,02</t>
+          <t>3,48; 32,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,47; 31,73</t>
+          <t>3,19; 27,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,52; 28,46</t>
+          <t>5,19; 27,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,6; 28,17</t>
+          <t>2,58; 25,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27; 16,58</t>
+          <t>1,27; 15,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,54; 32,0</t>
+          <t>10,76; 32,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 22,68</t>
+          <t>4,33; 23,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,53; 17,83</t>
+          <t>3,63; 17,06</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>6,57</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>1,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 1,88</t>
+          <t>-34,95; 2,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 24,4</t>
+          <t>-26,38; 24,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 26,48</t>
+          <t>-17,93; 26,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 12,28</t>
+          <t>-30,06; 11,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 43,43</t>
+          <t>-11,57; 41,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 18,44</t>
+          <t>-26,0; 16,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 2,4</t>
+          <t>-25,18; 2,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 24,95</t>
+          <t>-9,87; 25,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 16,1</t>
+          <t>-13,64; 16,1</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,13%</t>
+          <t>-6,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 19,7</t>
+          <t>-81,56; 25,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,11; 154,63</t>
+          <t>-64,27; 158,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 175,63</t>
+          <t>-41,35; 160,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 232,47</t>
+          <t>-75,26; 153,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 604,64</t>
+          <t>-33,81; 624,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 306,89</t>
+          <t>-70,36; 275,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 19,83</t>
+          <t>-67,69; 18,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 140,72</t>
+          <t>-30,02; 160,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 108,94</t>
+          <t>-39,42; 96,78</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-39,79</t>
+          <t>-40,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>15,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,53</t>
+          <t>-11,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 17,35</t>
+          <t>-38,35; 21,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-55,97; -6,2</t>
+          <t>-57,69; -7,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-62,98; -15,85</t>
+          <t>-62,6; -14,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 17,85</t>
+          <t>-24,72; 18,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 17,17</t>
+          <t>-24,42; 19,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 37,47</t>
+          <t>-7,98; 35,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 12,84</t>
+          <t>-26,17; 13,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-33,97; -0,23</t>
+          <t>-34,41; 0,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 6,96</t>
+          <t>-30,67; 3,39</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-73,89%</t>
+          <t>-75,35%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-28,64%</t>
+          <t>-31,7%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 52,25</t>
+          <t>-59,9; 53,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -13,53</t>
+          <t>-83,29; -13,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-93,42; -26,73</t>
+          <t>-92,48; -28,48</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 249,4</t>
+          <t>-83,36; 283,21</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 188,6</t>
+          <t>-83,3; 253,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 425,97</t>
+          <t>-28,94; 441,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 48,14</t>
+          <t>-58,38; 53,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-73,85; -0,05</t>
+          <t>-71,97; 6,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,52; 32,89</t>
+          <t>-64,11; 12,69</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 2,78</t>
+          <t>-17,21; 3,31</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -0,53</t>
+          <t>-22,03; -0,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 6,17</t>
+          <t>-16,81; 6,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,63</t>
+          <t>-12,59; 7,81</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,34</t>
+          <t>-14,48; 5,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 10,99</t>
+          <t>-9,74; 10,45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 1,56</t>
+          <t>-11,88; 2,37</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -0,61</t>
+          <t>-15,56; -0,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 4,63</t>
+          <t>-11,54; 4,16</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-17,27%</t>
+          <t>-16,46%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>-10,95%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 14,76</t>
+          <t>-42,74; 13,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-57,0; -2,3</t>
+          <t>-55,57; -2,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 22,92</t>
+          <t>-43,58; 25,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 47,86</t>
+          <t>-43,35; 55,98</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 39,07</t>
+          <t>-52,03; 35,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 75,82</t>
+          <t>-35,03; 73,75</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 7,78</t>
+          <t>-36,78; 11,36</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-48,46; -3,11</t>
+          <t>-47,54; -1,98</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 21,38</t>
+          <t>-34,36; 18,67</t>
         </is>
       </c>
     </row>
